--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00EBF3FC"/>
         <bgColor rgb="00EBF3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,15 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,32 +446,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Roll Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -489,64 +486,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>5023119</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>JADHAV ADITYA SUJIT</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>18:23:52</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Present</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SAWANT AKSHAT SANTOSH</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>18:46:20</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>KHAN ARSALAN AHMED</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>18:46:20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+          <t>06:09:41</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Present</t>
         </is>

--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -455,11 +455,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -494,21 +494,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5023113</v>
+        <v>5023104</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ASHLEY FERNANDES</t>
+          <t>Angella Benjamin</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:43:49</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -519,21 +519,21 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>5023112</v>
+        <v>5023102</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>kiera dcosta</t>
+          <t>AMAL BENNY</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:43:49</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -544,21 +544,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5023151</v>
+        <v>5023111</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SAWANT  AKSHAT SANTOSH</t>
+          <t>Aeldosh Dcosta</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:43:49</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -569,21 +569,21 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5023110</v>
+        <v>5023105</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DANNON ARULRAJ</t>
+          <t>Anvin Jose</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:43:49</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -594,21 +594,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5023101</v>
+        <v>5023112</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ALLEN ANTONY</t>
+          <t>kiera dcosta</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:44:12</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,21 +619,21 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5023104</v>
+        <v>5023101</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Angella Benjamin</t>
+          <t>ALLEN ANTONY</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:44:12</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -644,21 +644,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5023111</v>
+        <v>5023104</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Aeldosh Dcosta</t>
+          <t>Angella Benjamin</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:44:12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -669,21 +669,21 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5023115</v>
+        <v>5023102</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Riya Ramesh Gawde</t>
+          <t>AMAL BENNY</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>12:59:27</t>
+          <t>19:44:12</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -694,51 +694,351 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
+        <v>5023115</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Riya Ramesh Gawde</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19:44:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>5023111</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Aeldosh Dcosta</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>19:44:12</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>5023105</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Anvin Jose</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19:44:12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>5023113</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ASHLEY FERNANDES</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>19:44:12</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5023110</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DANNON ARULRAJ</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19:44:13</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>5023112</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>kiera dcosta</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>19:46:11</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>5023101</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ALLEN ANTONY</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19:46:11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>5023104</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Angella Benjamin</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>19:46:11</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
         <v>5023102</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>AMAL BENNY</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12:59:27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>5023105</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19:46:12</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>5023115</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Riya Ramesh Gawde</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>19:46:12</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>5023111</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Aeldosh Dcosta</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19:46:12</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>5023105</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Anvin Jose</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>12:59:27</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>19:46:12</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>5023113</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ASHLEY FERNANDES</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19:46:12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>5023110</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>DANNON ARULRAJ</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>19:46:12</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
